--- a/InputFiles/INS/TC13_INS_CancerType-Lymphoma.xlsx
+++ b/InputFiles/INS/TC13_INS_CancerType-Lymphoma.xlsx
@@ -1,223 +1,53 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11027"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/radhakrishnang2/Desktop/Automation/gayathri26sep/Commons_Automation/InputFiles/INS/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3827E68-F913-2C41-86E2-6E60FEA051A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="260" yWindow="760" windowWidth="25560" windowHeight="16260" xr2:uid="{8362173B-D28C-47E7-8626-98E16101E601}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="260" yWindow="760" windowWidth="25560" windowHeight="16260" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
-  <si>
-    <t>WebExcel</t>
-  </si>
-  <si>
-    <t>StatQuery</t>
-  </si>
-  <si>
-    <t>TabName</t>
-  </si>
-  <si>
-    <t>TabQuery</t>
-  </si>
-  <si>
-    <t>TsvExcel</t>
-  </si>
-  <si>
-    <t>ProgramsTab</t>
-  </si>
-  <si>
-    <t>ProjectsTab</t>
-  </si>
-  <si>
-    <t>GrantsTab</t>
-  </si>
-  <si>
-    <t>PublicationsTab</t>
-  </si>
-  <si>
-    <t>TC13_INS_CancerType-Lymphoma_TSVData.xlsx</t>
-  </si>
-  <si>
-    <t>TC13_INS_CancerType-Lymphoma_WebData.xlsx</t>
-  </si>
-  <si>
-    <t>SELECT DISTINCT
-    COUNT(DISTINCT prg.program_id) AS "Programs",
-    COUNT(DISTINCT prj.project_id) AS "Projects",
-    COUNT(DISTINCT gnt.grant_id) AS "Grants",
-    COUNT(DISTINCT pub.pmid) AS "Publications"
-FROM 
-    df_program prg
-LEFT JOIN 
-    df_project prj ON prg.program_id = prj."program.program_id"
-LEFT JOIN 
-    df_grant gnt ON prj.project_id = gnt."project.project_id"
-LEFT JOIN 
-    df_publication pub ON prj.project_id = pub."project.project_id"
-WHERE 
-    prg.cancer_type LIKE '%Lymphoma%';</t>
-  </si>
-  <si>
-    <t>SELECT DISTINCT 
-    prg.program_name AS "Program",
-  CASE
-    WHEN prg.program_link IS NOT NULL THEN prg.program_acronym
-        ELSE prg.program_link
-    END  AS "Website",
-    prg.focus_area AS "Special Topic",
-    prg.cancer_type AS "Cancer Type",
- CASE 
-        WHEN prg.data_link IS NOT NULL THEN prg.program_acronym     
-        ELSE prg.data_link
-    END AS "Data Location Details" 
-FROM 
-    df_program prg
-WHERE 
-     prg.cancer_type LIKE '%Lymphoma%'
-ORDER BY 
-    lower(prg.program_name) ASC
-LIMIT 100;</t>
-  </si>
-  <si>
-    <t>SELECT DISTINCT
-    prj.project_id AS "Project ID", 
-    prj.project_title AS "Project Title",
-    prj.project_org_name AS "Organization",
-    prj.project_start_date AS "Project Start Date",
-    prj.project_end_date AS "Project End Date"
-FROM 
-    df_project prj
-LEFT JOIN 
-    df_program prg ON prj."program.program_id" = prg.program_id
-LEFT JOIN 
-    df_grant gnt ON prj.project_id = gnt."project.project_id"
-LEFT JOIN 
-    df_publication pub ON prj.project_id = pub."project.project_id"
-WHERE 
-     prg.cancer_type LIKE '%Lymphoma%'
-ORDER BY 
-    lower(prj.project_id) ASC
-LIMIT 100;</t>
-  </si>
-  <si>
-    <t>SELECT DISTINCT
-    gnt.grant_id AS "Grant ID", 
-    prj.project_id AS "Project",
-    gnt.grant_title AS "Grant Title",
-    gnt.principal_investigators AS "Principal Investigators",
-    gnt.program_officers AS "Program Officers",
-    gnt.fiscal_year AS "Fiscal Year",
-    gnt.grant_end_date AS "Project End Date"
-FROM 
-    df_grant gnt
-LEFT JOIN 
-    df_project prj ON gnt."project.project_id" = prj.project_id
-LEFT JOIN 
-    df_program prg ON prj."program.program_id" = prg.program_id
-LEFT JOIN 
-    df_publication pub ON prj.project_id = pub."project.project_id"
-WHERE 
-    prg.cancer_type  LIKE '%Lymphoma%'
-ORDER BY 
-    lower(gnt.grant_id) ASC
-LIMIT 100;</t>
-  </si>
-  <si>
-    <t>SELECT DISTINCT
-    pub.pmid AS "PubMed ID", 
-    pub.publication_title AS "Title",
-    pub.authors AS "Authors",
-    pub.publication_date AS "Publication Date",
-    pub.cited_by AS "Cited By",
-    CASE 
-    WHEN pub.relative_citation_ratio = 0 THEN '0'
-    WHEN pub.relative_citation_ratio = 7.0 THEN '7'
-    WHEN pub.relative_citation_ratio = 2.0 THEN '2'
-  WHEN pub.relative_citation_ratio = 1.0 THEN '1'
-    WHEN pub.relative_citation_ratio = ROUND(pub.relative_citation_ratio) THEN CAST(ROUND(pub.relative_citation_ratio) AS VARCHAR) 
-    ELSE CAST(ROUND(pub.relative_citation_ratio, 2) AS VARCHAR)
-END AS "Relative Citation Ratio"
-FROM 
-    df_publication pub
-LEFT JOIN 
-    df_project prj ON pub."project.project_id" = prj.project_id
-LEFT JOIN 
-    df_program prg ON prj."program.program_id" = prg.program_id
-LEFT JOIN 
-    df_grant gnt ON prj.project_id = gnt."project.project_id"
-WHERE 
-     prg.cancer_type  LIKE '%Lymphoma%'
-ORDER BY 
-    lower(pub.pmid) ASC
-LIMIT 100;</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="4">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color indexed="8"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <sz val="8"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -237,28 +67,87 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{7EA68BB1-159D-4F44-96A3-D0B7FBE8815D}"/>
+    <cellStyle name="Normal 2" xfId="1"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -558,87 +447,218 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C538400-E87C-4027-A918-A51DB80B3430}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="75.83203125" customWidth="1"/>
-    <col min="3" max="3" width="60.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="45.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="46.33203125" bestFit="1" customWidth="1"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="75.83203125" customWidth="1" min="2" max="2"/>
+    <col width="60.83203125" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="45.5" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="46.33203125" bestFit="1" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" t="s">
-        <v>0</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>TabName</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>TabQuery</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>StatQuery</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>TsvExcel</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>WebExcel</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="242" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
+    <row r="2" ht="242" customHeight="1">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ProgramsTab</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>SELECT DISTINCT 
+    prg.program_name AS "Program",
+  CASE
+    WHEN prg.program_link IS NOT NULL THEN prg.program_acronym
+        ELSE prg.program_link
+    END  AS "Website",
+    prg.focus_area AS "Special Topic",
+    prg.cancer_type AS "Cancer Type",
+ CASE 
+        WHEN prg.data_link IS NOT NULL THEN prg.program_acronym     
+        ELSE prg.data_link
+    END AS "Data Location Details" 
+FROM 
+    df_program prg
+WHERE 
+     prg.cancer_type LIKE '%Lymphoma%'
+ORDER BY 
+    lower(prg.program_name) ASC
+LIMIT 100;</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>SELECT DISTINCT
+    COUNT(DISTINCT prg.program_id) AS "Programs",
+    COUNT(DISTINCT prj.project_id) AS "Projects",
+    COUNT(DISTINCT gnt.grant_id) AS "Grants",
+    COUNT(DISTINCT pub.pmid) AS "Publications"
+FROM 
+    df_program prg
+LEFT JOIN 
+    df_project prj ON prg.program_id = prj."program.program_id"
+LEFT JOIN 
+    df_grant gnt ON prj.project_id = gnt."project.project_id"
+LEFT JOIN 
+    df_publication pub ON prj.project_id = pub."project.project_id"
+WHERE 
+    prg.cancer_type LIKE '%Lymphoma%';</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>TC13_INS_CancerType-Lymphoma_TSVData.xlsx</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TC13_INS_CancerType-Lymphoma_WebData.xlsx</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="307" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>13</v>
+    <row r="3" ht="307" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ProjectsTab</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>SELECT DISTINCT
+    prj.project_id AS "Project ID", 
+    prj.project_title AS "Project Title",
+    prj.project_org_name AS "Organization",
+    prj.project_start_date AS "Project Start Date",
+    prj.project_end_date AS "Project End Date"
+FROM 
+    df_project prj
+LEFT JOIN 
+    df_program prg ON prj."program.program_id" = prg.program_id
+LEFT JOIN 
+    df_grant gnt ON prj.project_id = gnt."project.project_id"
+LEFT JOIN 
+    df_publication pub ON prj.project_id = pub."project.project_id"
+WHERE 
+     prg.cancer_type LIKE '%Lymphoma%'
+ORDER BY 
+    lower(prj.project_id) ASC
+LIMIT 100;</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="356" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="2"/>
+    <row r="4" ht="356" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>GrantsTab</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>SELECT DISTINCT
+    gnt.grant_id AS "Grant ID", 
+    prj.project_id AS "Project",
+    gnt.grant_title AS "Grant Title",
+    gnt.principal_investigators AS "Principal Investigators",
+    gnt.program_officers AS "Program Officers",
+    gnt.fiscal_year AS "Fiscal Year",
+    gnt.grant_end_date AS "Project End Date"
+FROM 
+    df_grant gnt
+LEFT JOIN 
+    df_project prj ON gnt."project.project_id" = prj.project_id
+LEFT JOIN 
+    df_program prg ON prj."program.program_id" = prg.program_id
+LEFT JOIN 
+    df_publication pub ON prj.project_id = pub."project.project_id"
+WHERE 
+    prg.cancer_type  LIKE '%Lymphoma%'
+ORDER BY 
+    lower(gnt.grant_id) ASC
+LIMIT 100;</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n"/>
     </row>
-    <row r="5" spans="1:5" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="2"/>
+    <row r="5" ht="409.6" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PublicationsTab</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>SELECT DISTINCT
+    pub.pmid AS "PubMed ID", 
+    pub.publication_title AS "Title",
+    pub.authors AS "Authors",
+    pub.publication_date AS "Publication Date",
+    pub.cited_by AS "Cited By",
+    CASE 
+    WHEN pub.relative_citation_ratio = 0 THEN '0'
+    WHEN pub.relative_citation_ratio = 7.0 THEN '7'
+    WHEN pub.relative_citation_ratio = 2.0 THEN '2'
+  WHEN pub.relative_citation_ratio = 1.0 THEN '1'
+    WHEN pub.relative_citation_ratio = ROUND(pub.relative_citation_ratio) THEN CAST(ROUND(pub.relative_citation_ratio) AS VARCHAR) 
+    ELSE CAST(ROUND(pub.relative_citation_ratio, 3) AS VARCHAR)
+END AS "Relative Citation Ratio"
+FROM 
+    df_publication pub
+LEFT JOIN 
+    df_project prj ON pub."project.project_id" = prj.project_id
+LEFT JOIN 
+    df_program prg ON prj."program.program_id" = prg.program_id
+LEFT JOIN 
+    df_grant gnt ON prj.project_id = gnt."project.project_id"
+WHERE 
+     prg.cancer_type  LIKE '%Lymphoma%'
+ORDER BY 
+    lower(pub.pmid) ASC
+LIMIT 100;</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
+    <row r="6">
+      <c r="B6" s="1" t="n"/>
+      <c r="C6" s="1" t="n"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="C7" s="1"/>
+    <row r="7">
+      <c r="C7" s="1" t="n"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
 </worksheet>
 </file>